--- a/SensitivityAnalysis/LeaveOneOut/ContinuousData/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/ContinuousData/loo.xlsx
@@ -17,12 +17,24 @@
     <sheet name="30750-0.0" r:id="rId11" sheetId="9"/>
     <sheet name="30740-0.0" r:id="rId12" sheetId="10"/>
     <sheet name="30780-0.0" r:id="rId13" sheetId="11"/>
+    <sheet name="Sheet11" r:id="rId14" sheetId="12"/>
+    <sheet name="Sheet12" r:id="rId15" sheetId="13"/>
+    <sheet name="Sheet13" r:id="rId16" sheetId="14"/>
+    <sheet name="Sheet14" r:id="rId17" sheetId="15"/>
+    <sheet name="Sheet15" r:id="rId18" sheetId="16"/>
+    <sheet name="Sheet16" r:id="rId19" sheetId="17"/>
+    <sheet name="Sheet17" r:id="rId20" sheetId="18"/>
+    <sheet name="Sheet18" r:id="rId21" sheetId="19"/>
+    <sheet name="Sheet19" r:id="rId22" sheetId="20"/>
+    <sheet name="Sheet20" r:id="rId23" sheetId="21"/>
+    <sheet name="Sheet21" r:id="rId24" sheetId="22"/>
+    <sheet name="Sheet22" r:id="rId25" sheetId="23"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="22">
   <si>
     <t>SNPS</t>
   </si>
@@ -83,6 +95,12 @@
   <si>
     <t>rs80107551</t>
   </si>
+  <si>
+    <t>CI_LOW</t>
+  </si>
+  <si>
+    <t>CI_HIGH</t>
+  </si>
 </sst>
 </file>
 
@@ -700,6 +718,1542 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.931909497717575</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7205324435091726</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.1432865519259776</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.10784543582061351</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.5645886360716805E-18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.1036146599961594</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9948732416408018</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.212356078351517</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05548031548742733</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.772904888565285E-88</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0790210334205437</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7758044558971378</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.3822376109439496</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1547023354711255</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.062614145254206E-12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7868648588199109</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5844159680312841</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9893137496085376</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1032902504023606</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.5764149098300926E-14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9303581359657095</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6932669036535268</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.1674493682778921</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.12096491444499118</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.458293396460425E-14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8484298115366344</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6468308759707988</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.05002874710247</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.10285659977848759</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.6017144633827882E-16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.926502393831458</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.694700918220645</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.1583038694422712</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.11826605898510875</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.723952329451961E-15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.931909497717575</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7205324435091726</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.1432865519259776</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.10784543582061351</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.5645886360716805E-18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.1036146599961594</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9948732416408018</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.212356078351517</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05548031548742733</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.772904888565285E-88</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0790210334205437</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7758044558971378</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.3822376109439496</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1547023354711255</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.062614145254206E-12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7868648588199109</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5844159680312841</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9893137496085376</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1032902504023606</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.5764149098300926E-14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9303581359657095</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6932669036535268</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.1674493682778921</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.12096491444499118</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.458293396460425E-14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8484298115366344</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6468308759707988</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.05002874710247</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.10285659977848759</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.6017144633827882E-16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.926502393831458</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.694700918220645</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.1583038694422712</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.11826605898510875</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.723952329451961E-15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.03574643494360698</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-9.362342688830558E-4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.07242910415609702</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.018715647557392873</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.056136322200357816</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.03788802322449598</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.008300182404774835</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.08407622885376678</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02356541103534225</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.10788312224833592</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0210755084763154</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.03460512455320848</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07675614150583929</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.028408486239553003</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.45816386868009784</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.02330092790822724</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.02382467943685371</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.07042653525330819</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.024043677216878036</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.33249114127995855</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.03592884876278468</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-9.47355027298924E-4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.07280505255286829</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.018814389688818167</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.056178638620242236</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.03277163786907704</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.008695338254828752</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.07423861399298283</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021156620471380505</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.12138134785585086</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.03824289144676515</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.001369041742082265</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07511674115144804</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.018813188624838207</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.04207573311274741</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05915991830250599</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.017502068484797483</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.10081776812021451</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.021254005009034953</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005378057859113937</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.07383252297541545</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.020174186268397523</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1274908596824334</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.027376702401539763</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.006998602540540138</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.06008411711873482</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.010602424843004402</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.13077065908047403</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.036064562225377156</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.09571034133547288</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.03334772661850328</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.014387893530977601</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.08108334676798415</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.02435490823953106</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.17092411156594092</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.05932116226417794</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.012526049084507385</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1061162754438485</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.023875057744729877</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.012967886176374809</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04367817123843474</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0016742090306944638</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.08568213344617501</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021430592963132794</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.041537695036630046</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.06228971549915245</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.02493835687245556</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.09964107412584934</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01905681562586576</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.00108068793473313</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.2237771824735491</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.30798399463634796</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.13957037031075026</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0429626592667341</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.902260466411541E-7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.255000235497851</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.36231052729206187</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.14768994370364014</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05475014887459738</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.200321976539395E-6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.2806620317265825</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.4028510227756668</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.15847304067749818</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.06234132196381854</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.730986624013611E-6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.1789547426811224</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.27762403989752127</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.08028544546472352</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.050341478171632086</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.7824224186246147E-4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.2245417779223599</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3189007540209645</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.1301828018237553</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.048142334744186034</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.099357426874473E-6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.17636520822077706</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2165434513845057</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.13618696505704841</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.020499103654963588</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.728279681350265E-18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.22738540533078497</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.31539113848878664</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.1393796721727833</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04490088426428656</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.101981570949229E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.2812374948697123</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.20488944667524825</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.35758554306417634</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.038953085813502056</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.202473156067034E-13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.3173269449858093</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.22697045380371678</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.40768343616790187</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.046100250603108434</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.843635417069699E-12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3028813031924378</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1764188658600705</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.42934374052480506</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0645216517001874</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.675756816353185E-6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2279578194451356</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1564957494077181</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2994198894825531</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.03646023981500894</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.046318785865935E-10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2822101172910578</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.19690737446284876</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.36751286011926687</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.043521807565412796</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.912213482755919E-11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.24510061682398304</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.18557860667744114</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.30462262697052495</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.030368372523745878</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.977208568845532E-16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.28537937399746277</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.20941898419161908</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.36133976380330646</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.038755300921348816</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.7898649647692223E-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.15092675330312147</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.22466237309051135</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.0771911335157316</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03762021417723973</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.024411777590431E-5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.16936339486517427</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.2688085477686283</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.06991824196172024</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.050737322909925525</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.437051631537243E-4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.20968932450422723</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.30867514834060994</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.11070350066784453</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05050297134509321</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.295540969296039E-5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.12063569370627553</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.21541481326924844</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.025856574143302627</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04835669365457801</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.012606182450557162</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.15102008038368772</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.23388938150984118</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.06815077925753427</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.042280255676608904</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.544252291696689E-4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.1102128461308563</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1510898514728174</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.06933584078889522</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.020855614970388306</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.2600402911205414E-7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.15428962426236992</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.2305449711433638</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.07803427738137601</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03890578922499689</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.317347859252314E-5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.12179124549771227</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0712413738363865</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.17234111715903805</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.025790750847615188</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.3321091923976777E-6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.14193362279383384</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.07862172665337341</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.20524551893429427</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03230198782676553</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.1130461588914655E-5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.13097587098617386</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.046030252000322805</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.21592148997202493</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.043339601523393396</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.002510417419464597</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.08873067323848802</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.037664705442111916</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1397966410348641</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.026054065202232704</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.601002563641802E-4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.12195729256367031</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.06516468084705548</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.17874990428028514</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.028975822304395323</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.565795339292935E-5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.10045632591607576</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05494718246013619</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.14596546937201532</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.02321895074282631</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.5151107245201292E-5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.12529923753747682</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.07963078922584929</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.17096768584910435</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.023300228730422208</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.548659265496716E-8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -885,6 +2439,774 @@
       </c>
       <c r="G8" t="n">
         <v>0.04207573311274741</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.02943254833946728</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.00789026014729145</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.066755356826226</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.019042249227938127</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.12219044078354165</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.006038298431212163</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.0409549285530711</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.05303152541549542</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02397613621647105</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8011599573113087</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.011005415510499347</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.045646480797575044</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.06765731181857373</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.028904028728609383</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7033834600870473</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.05464478722882384</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.006696282401525887</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1025932920561218</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.024463522871070387</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02550116061670136</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.029695401088564846</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.007824399891831528</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06721520206896123</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.019142755602243048</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.12083926297411568</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04213990920617099</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-5.082730421731435E-5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0843306457165593</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021525885974687912</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05027241324072354</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.029147255258514443</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.00837006480121967</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.06666457531824856</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.019141489826394957</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.12782712622792985</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.020269808751112006</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.06211246090909776</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.021572843406873744</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.021348291917339668</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.342375764385139</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.015680918185453085</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.06835413254279454</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.03699229617188837</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.026874088957827277</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5595595798493709</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.00810748296966204</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.0716198035736233</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.05540483763429921</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03240424520610268</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8024340975533453</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.023408393025224284</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.07717749819161647</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0303607121411679</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.027433216921628666</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.39350045729598154</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.017335616910070125</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.05939843562262746</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.024727201802487216</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.021460621792121094</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.419213059446973</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.024189970211720948</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.07149534056678505</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.023115400143343155</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.024135393038298012</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3162174121932439</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.023949049765005493</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.06600981755946653</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.018111718029455545</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.021459575405337265</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.26441887108359746</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.018562677370012253</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.018815966845103612</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.055941321585128115</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01907073684444687</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3303748037030675</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.011891371872790915</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.035168112073870966</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.058950855819452794</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.024009940789113206</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6204104704899701</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.04225276108653526</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.014478207509115118</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.09898372968218563</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02894437173247468</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.14434725941906212</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.03117431265869525</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.01684904098362845</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.07919766630101895</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.024501711042001887</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2032551596167816</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.01591760197115121</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.02165838299449708</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0534935869367995</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.019171420900840966</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.40638183097990344</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.01936384861414428</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.022890962327029543</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0616186595553181</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021558577010802972</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3690805468693195</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01907338960360021</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.018500373993472412</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.05664715320067283</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01917028754952685</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.31976281558183184</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.08969700388260139</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.05056345920535811</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.12883054855984466</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01996609422308331</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.0403087638715485E-6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.10284315912275133</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.053570179412439495</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.15211613883306316</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.025139275362403995</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.2963624260596356E-5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.11023901809636232</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.050838782479662226</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1696392537130624</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03030624266158168</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.7529506229688374E-4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.08110647114016263</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.030829458900992812</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.13138348337933245</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.025651536856719295</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0015676695212573808</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.08772151477965855</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.048381481117834184</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1270615484414829</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.020071445745828757</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.2398325551345761E-5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.08351903680913872</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.03928048971589261</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.12775758390238484</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.022570687292472504</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.153175725380216E-4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0902197469488535</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.05088250484816266</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.12955698904954432</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.020070021479944307</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.948853523270882E-6</v>
       </c>
     </row>
   </sheetData>

--- a/SensitivityAnalysis/LeaveOneOut/ContinuousData/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/ContinuousData/loo.xlsx
@@ -29,12 +29,23 @@
     <sheet name="Sheet20" r:id="rId23" sheetId="21"/>
     <sheet name="Sheet21" r:id="rId24" sheetId="22"/>
     <sheet name="Sheet22" r:id="rId25" sheetId="23"/>
+    <sheet name="Sheet23" r:id="rId26" sheetId="24"/>
+    <sheet name="Sheet24" r:id="rId27" sheetId="25"/>
+    <sheet name="Sheet25" r:id="rId28" sheetId="26"/>
+    <sheet name="Sheet26" r:id="rId29" sheetId="27"/>
+    <sheet name="Sheet27" r:id="rId30" sheetId="28"/>
+    <sheet name="Sheet28" r:id="rId31" sheetId="29"/>
+    <sheet name="Sheet29" r:id="rId32" sheetId="30"/>
+    <sheet name="Sheet30" r:id="rId33" sheetId="31"/>
+    <sheet name="Sheet31" r:id="rId34" sheetId="32"/>
+    <sheet name="Sheet32" r:id="rId35" sheetId="33"/>
+    <sheet name="Sheet33" r:id="rId36" sheetId="34"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="22">
   <si>
     <t>SNPS</t>
   </si>
@@ -3214,6 +3225,1158 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.931909497717575</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7205324435091726</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.1432865519259776</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.10784543582061351</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.5645886360716805E-18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.1036146599961594</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9948732416408018</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.212356078351517</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05548031548742733</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.772904888565285E-88</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0790210334205437</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7758044558971378</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.3822376109439496</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1547023354711255</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.062614145254206E-12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7868648588199109</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5844159680312841</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9893137496085376</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1032902504023606</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.5764149098300926E-14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9303581359657095</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6932669036535268</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.1674493682778921</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.12096491444499118</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.458293396460425E-14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8484298115366344</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6468308759707988</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.05002874710247</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.10285659977848759</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.6017144633827882E-16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.926502393831458</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.694700918220645</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.1583038694422712</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.11826605898510875</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.723952329451961E-15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.03574643494360698</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-9.362342688830558E-4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.07242910415609702</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.018715647557392873</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.056136322200357816</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.03788802322449598</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.008300182404774835</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.08407622885376678</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02356541103534225</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.10788312224833592</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0210755084763154</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.03460512455320848</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07675614150583929</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.028408486239553003</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.45816386868009784</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.02330092790822724</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.02382467943685371</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.07042653525330819</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.024043677216878036</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.33249114127995855</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.03592884876278468</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-9.47355027298924E-4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.07280505255286829</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.018814389688818167</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.056178638620242236</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.03277163786907704</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.008695338254828752</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.07423861399298283</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021156620471380505</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.12138134785585086</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.03824289144676515</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.001369041742082265</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07511674115144804</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.018813188624838207</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.04207573311274741</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05915991830250599</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.017502068484797483</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.10081776812021451</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.021254005009034953</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005378057859113937</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.07383252297541545</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.020174186268397523</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1274908596824334</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.027376702401539763</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.006998602540540138</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.06008411711873482</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.010602424843004402</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.13077065908047403</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.036064562225377156</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.09571034133547288</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.03334772661850328</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.014387893530977601</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.08108334676798415</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.02435490823953106</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.17092411156594092</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.05932116226417794</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.012526049084507385</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1061162754438485</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.023875057744729877</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.012967886176374809</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04367817123843474</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0016742090306944638</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.08568213344617501</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021430592963132794</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.041537695036630046</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.06228971549915245</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.02493835687245556</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.09964107412584934</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01905681562586576</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.00108068793473313</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.2237771824735491</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.30798399463634796</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.13957037031075026</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0429626592667341</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.902260466411541E-7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.255000235497851</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.36231052729206187</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.14768994370364014</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05475014887459738</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.200321976539395E-6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.2806620317265825</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.4028510227756668</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.15847304067749818</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.06234132196381854</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.730986624013611E-6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.1789547426811224</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.27762403989752127</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.08028544546472352</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.050341478171632086</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.7824224186246147E-4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.2245417779223599</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3189007540209645</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.1301828018237553</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.048142334744186034</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.099357426874473E-6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.17636520822077706</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2165434513845057</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.13618696505704841</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.020499103654963588</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.728279681350265E-18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.22738540533078497</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.31539113848878664</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.1393796721727833</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04490088426428656</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.101981570949229E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.2812374948697123</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.20488944667524825</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.35758554306417634</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.038953085813502056</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.202473156067034E-13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.3173269449858093</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.22697045380371678</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.40768343616790187</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.046100250603108434</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.843635417069699E-12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3028813031924378</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1764188658600705</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.42934374052480506</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0645216517001874</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.675756816353185E-6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2279578194451356</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1564957494077181</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2994198894825531</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.03646023981500894</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.046318785865935E-10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2822101172910578</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.19690737446284876</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.36751286011926687</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.043521807565412796</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.912213482755919E-11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.24510061682398304</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.18557860667744114</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.30462262697052495</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.030368372523745878</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.977208568845532E-16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.28537937399746277</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.20941898419161908</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.36133976380330646</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.038755300921348816</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.7898649647692223E-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.15092675330312147</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.22466237309051135</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.0771911335157316</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03762021417723973</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.024411777590431E-5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.16936339486517427</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.2688085477686283</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.06991824196172024</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.050737322909925525</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.437051631537243E-4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.20968932450422723</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.30867514834060994</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.11070350066784453</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05050297134509321</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.295540969296039E-5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.12063569370627553</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.21541481326924844</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.025856574143302627</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04835669365457801</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.012606182450557162</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.15102008038368772</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.23388938150984118</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.06815077925753427</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.042280255676608904</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.544252291696689E-4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.1102128461308563</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1510898514728174</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.06933584078889522</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.020855614970388306</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.2600402911205414E-7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.15428962426236992</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.2305449711433638</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.07803427738137601</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03890578922499689</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.317347859252314E-5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -3399,6 +4562,966 @@
       </c>
       <c r="G8" t="n">
         <v>4.101981570949229E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.12179124549771227</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0712413738363865</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.17234111715903805</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.025790750847615188</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.3321091923976777E-6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.14193362279383384</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.07862172665337341</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.20524551893429427</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03230198782676553</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.1130461588914655E-5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.13097587098617386</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.046030252000322805</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.21592148997202493</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.043339601523393396</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.002510417419464597</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.08873067323848802</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.037664705442111916</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1397966410348641</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.026054065202232704</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.601002563641802E-4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.12195729256367031</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.06516468084705548</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.17874990428028514</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.028975822304395323</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.565795339292935E-5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.10045632591607576</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05494718246013619</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.14596546937201532</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.02321895074282631</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.5151107245201292E-5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.12529923753747682</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.07963078922584929</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.17096768584910435</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.023300228730422208</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.548659265496716E-8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.02943254833946728</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.00789026014729145</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.066755356826226</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.019042249227938127</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.12219044078354165</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.006038298431212163</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.0409549285530711</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.05303152541549542</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02397613621647105</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8011599573113087</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.011005415510499347</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.045646480797575044</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.06765731181857373</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.028904028728609383</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7033834600870473</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.05464478722882384</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.006696282401525887</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1025932920561218</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.024463522871070387</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02550116061670136</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.029695401088564846</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.007824399891831528</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06721520206896123</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.019142755602243048</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.12083926297411568</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04213990920617099</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-5.082730421731435E-5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0843306457165593</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021525885974687912</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05027241324072354</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.029147255258514443</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.00837006480121967</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.06666457531824856</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.019141489826394957</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.12782712622792985</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.020269808751112006</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.06211246090909776</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.021572843406873744</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.021348291917339668</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.342375764385139</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.015680918185453085</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.06835413254279454</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.03699229617188837</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.026874088957827277</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5595595798493709</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.00810748296966204</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.0716198035736233</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.05540483763429921</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03240424520610268</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8024340975533453</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.023408393025224284</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.07717749819161647</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0303607121411679</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.027433216921628666</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.39350045729598154</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.017335616910070125</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.05939843562262746</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.024727201802487216</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.021460621792121094</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.419213059446973</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.024189970211720948</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.07149534056678505</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.023115400143343155</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.024135393038298012</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3162174121932439</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.023949049765005493</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.06600981755946653</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.018111718029455545</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.021459575405337265</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.26441887108359746</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.018562677370012253</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.018815966845103612</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.055941321585128115</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01907073684444687</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3303748037030675</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.011891371872790915</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.035168112073870966</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.058950855819452794</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.024009940789113206</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6204104704899701</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.04225276108653526</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.014478207509115118</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.09898372968218563</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02894437173247468</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.14434725941906212</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.03117431265869525</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.01684904098362845</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.07919766630101895</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.024501711042001887</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2032551596167816</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.01591760197115121</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.02165838299449708</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0534935869367995</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.019171420900840966</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.40638183097990344</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.01936384861414428</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.022890962327029543</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0616186595553181</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021558577010802972</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3690805468693195</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01907338960360021</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.018500373993472412</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.05664715320067283</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01917028754952685</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.31976281558183184</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.08969700388260139</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.05056345920535811</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.12883054855984466</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01996609422308331</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.0403087638715485E-6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.10284315912275133</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.053570179412439495</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.15211613883306316</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.025139275362403995</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.2963624260596356E-5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.11023901809636232</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.050838782479662226</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1696392537130624</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03030624266158168</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.7529506229688374E-4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.08110647114016263</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.030829458900992812</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.13138348337933245</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.025651536856719295</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0015676695212573808</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.08772151477965855</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.048381481117834184</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1270615484414829</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.020071445745828757</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.2398325551345761E-5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.08351903680913872</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.03928048971589261</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.12775758390238484</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.022570687292472504</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.153175725380216E-4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0902197469488535</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.05088250484816266</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.12955698904954432</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.020070021479944307</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.948853523270882E-6</v>
       </c>
     </row>
   </sheetData>

--- a/SensitivityAnalysis/LeaveOneOut/ContinuousData/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/ContinuousData/loo.xlsx
@@ -40,12 +40,23 @@
     <sheet name="Sheet31" r:id="rId34" sheetId="32"/>
     <sheet name="Sheet32" r:id="rId35" sheetId="33"/>
     <sheet name="Sheet33" r:id="rId36" sheetId="34"/>
+    <sheet name="Sheet34" r:id="rId37" sheetId="35"/>
+    <sheet name="Sheet35" r:id="rId38" sheetId="36"/>
+    <sheet name="Sheet36" r:id="rId39" sheetId="37"/>
+    <sheet name="Sheet37" r:id="rId40" sheetId="38"/>
+    <sheet name="Sheet38" r:id="rId41" sheetId="39"/>
+    <sheet name="Sheet39" r:id="rId42" sheetId="40"/>
+    <sheet name="Sheet40" r:id="rId43" sheetId="41"/>
+    <sheet name="Sheet41" r:id="rId44" sheetId="42"/>
+    <sheet name="Sheet42" r:id="rId45" sheetId="43"/>
+    <sheet name="Sheet43" r:id="rId46" sheetId="44"/>
+    <sheet name="Sheet44" r:id="rId47" sheetId="45"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="22">
   <si>
     <t>SNPS</t>
   </si>
@@ -5529,6 +5540,966 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9024547199379768</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6988511058256401</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.1060583340503134</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1038793949552738</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.704247082827798E-18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0615655855847823</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.941677684868489</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.1814534863010755</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.061167296283823086</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.8043238768196608E-67</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0392177919476093</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7454630160224065</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.3329725678728122</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.14987488567612386</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.09387877777535E-12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7570550816577252</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5849878057299895</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9291223575854608</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0877894264937427</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.491903499510489E-18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9047213384267564</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6755292724528003</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.1339134044007126</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.11693472753773272</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.0180818710777864E-14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8163875059052333</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.647537526411686</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9852374853987806</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.08614794872119759</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.6276602287339895E-21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8976463053962972</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.672601571334284</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.1226910394583105</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.11481874186837408</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.3693766558318525E-15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.033451526838699897</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.0020579658081790048</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0689610194855788</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.018117088085142296</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.06483306289084438</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.03466441268667142</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.00983011242156294</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.07915893779490578</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.022701288320527736</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.12676599076932626</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.01779557141116915</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.035849327660994475</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07144047048333277</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.027369846465389605</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.51557018549394</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.020817614971215995</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.02419753094194857</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.06583276088438056</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.022966911180186</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3647148039959031</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.03383293824788485</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.0020128709574287335</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06967874745319844</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01828867816597632</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0643223479117234</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.030069110269546413</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.009560154994556185</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.069698375533649</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.020219012889848266</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.13696990594107264</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.03609842624594196</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.7065501324402145E-4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07182619747863989</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01822845471056017</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.04766602544320516</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.055581311238197005</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.01348156164867359</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.09768106082772042</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.021479464076287456</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.009663342525929413</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.068292767025182</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.013055151778703089</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.12353038227166091</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02818245675840761</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.015382894709672655</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.054031816656474684</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.01704820732023015</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1251118406331795</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03626531835546165</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.13624966982811157</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.029992960145184194</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.01560496739255653</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.07559088768292492</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.023264248743745268</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.19731824685477212</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.05603332914414476</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.008629319305423017</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1034373389828665</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.024185719305470275</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.020514956558075646</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0405525111655574</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.7663349090466657E-4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.08128165582201946</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.020780175845133707</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05099760762531719</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.05891017559019629</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.021909914731915073</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0959104364484775</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01887768411136797</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0018046760249190788</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.2133382117160196</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.3012574055248699</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.12541901790716933</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04485673153512769</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.9747526195382063E-6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.24010814152872803</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.3553217500139873</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.12489453304346877</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05878245330880574</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.413556300222257E-5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.26245644040106103</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.3963510601240718</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.12856182067805028</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.06831358149133201</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.2206743301971085E-4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.16716361657319484</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.2677147148704013</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.06661251827598835</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.05130158076388086</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0011202276313116745</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.21530854595434035</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3135249306885651</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.11709216122011562</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.05011040037460445</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.7337221540684154E-5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.16726405901752003</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2084306905507913</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.12609742748424876</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021003383435342485</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.6700743575135175E-15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.2173050400217678</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.3097091576812443</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.1249009223622913</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04714495798952882</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.04035839553752E-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.2689825449182953</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.18641241173551004</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3515526781010806</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.042127618970808814</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.7145868829752514E-10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.30012230141124374</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.19612191750556718</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4041226853169203</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05306142036003907</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.5482404938541995E-8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2841973444870471</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.14615978459017218</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.42223490438392197</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0704273264779974</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.452613092753949E-5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2142972846404047</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.13624702292382246</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.29234754635698695</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.039821562100297074</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.389297788078343E-8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.27149058978230917</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.18005233589230593</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3629288436723124</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.046652170352042464</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.903691048685539E-9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.23235761997250445</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1684946451908848</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2962205947541241</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.03258315039878553</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9.948302269702263E-13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2735656672985577</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.19006736929326679</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3570639653038486</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04260117245167903</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.3489143666201435E-10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -5714,6 +6685,1158 @@
       </c>
       <c r="G8" t="n">
         <v>1.7898649647692223E-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.14342688924425157</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.21885737412627332</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.0679964043622298</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.038484941266337634</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.9390203610419114E-4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.15872791708643036</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.2614236100212129</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.056032224151647825</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.052395761701419664</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0024503696688550013</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.19545247129839224</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.30317748584306925</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.08772745675371524</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.054961742114631125</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.763221763331378E-4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.11194961842470176</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.20635967071738126</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.017539566132022275</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04816839402687729</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02011851779766601</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.14419667529952565</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.2291505797171936</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.05924277088185771</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04334382878452446</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.784630449741495E-4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.10439090675400242</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.14345670596254068</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.06532510754546417</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.01993153020843788</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.6278765362988658E-7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.1470746464150195</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.22548751258393346</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.06866178024610554</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04000656437189487</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.3667566459912762E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.11582840366459313</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.06324012506347912</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.16841668226570713</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.02683075438832347</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.581631714421938E-5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.13323079697624382</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.06521412715688417</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.20124746679560346</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03470238256089778</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.234154308188197E-4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.12139680170676898</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.03287533286499045</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2099182705485475</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04516401471519313</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.007190079723865843</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.08253277307254744</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.030221350535278926</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.13484419560981598</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.026689501294524753</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001985912546626438</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.11656972007988262</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.05745540821772376</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.17568403194204146</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.030160363194979008</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.1109046225922365E-4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0946998160314348</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.048545249585816005</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.14085438247705362</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.023548248186540204</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.7823119733782613E-5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.11960935754130539</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.07089302072965702</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.16832569435295375</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.024855273883494067</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.4925355046389127E-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.028676763667937564</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.007452275193863964</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0648058025297391</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01843318309275588</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.11977608157812868</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.006405997276235714</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.03886387156758277</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.05167586612005419</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02309687185909106</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7815087154430339</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.011175899636077654</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.04340443915425403</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.06575623842640933</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.027847111627720245</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6881766945539827</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.051685215175180974</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.005884297075569533</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.09748613327479241</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.023367815356944613</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.026979655386432766</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.029159300684715186</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.007312047998733119</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06563064936816349</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.018607830960943015</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.11710427134527374</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.03978539974543926</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-5.353559705801314E-4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.08010615546145865</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.02057181414082622</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05311604933070036</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.028406381948008423</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.007944733237179702</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.06475749713319655</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.018546487339381697</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.12561342502607048</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.019859149202571848</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.060364076719724775</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.02064577831458108</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.020665779345486187</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3365683416443059</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.015537579123532087</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.0662809238165445</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.035205765569480324</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.025889461578067558</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5484057898052688</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.00845110728427604</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.06964362251807699</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.052741407949524914</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03122067103765355</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7866298667236552</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.022644548141675717</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.07400571103315437</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.028716614749802933</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.026204674944631964</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3875101422736684</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.016131180401057495</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.057018839536366585</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.024756478734251595</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.020861050579239333</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.43936385952752643</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.023196596661606124</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.06840572807837708</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02201253475516484</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.023065883375903554</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3145758049273175</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.023753865862684156</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.06450785728139477</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.017000125556026455</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.020792852764648272</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2532855760279903</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.019042154019356005</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.017140760913123696</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.05522506895183571</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.018460670883918215</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.30230711905110785</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.013225272292823265</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.032108162660640024</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.05855870724628656</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.023129303547685356</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5674593367703831</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.04296466096128604</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.011690959558604302</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.09762028148117638</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02788552067341344</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.12337724991026425</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.031097871567493822</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.014773837200803323</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.07696958033579096</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.023403933045049563</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.18393193614026063</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.015700120043045145</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.020825709088548233</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05222594917463852</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.018635627107955806</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.39952002303144035</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.019803333334849196</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.020578281944540047</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.06018494861423844</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0206028649384639</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3364550432372548</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01961038442615284</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.016795305974888434</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.05601607482719412</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.018574331837265957</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.29106931926822766</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.08742346424326687</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.04954116689058179</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.12530576159595194</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.019327702730961776</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.090568589478632E-6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.09984259509665767</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.05237582346685841</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.14730936672645695</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.024217740627448605</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.744494685158005E-5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.10740298798341016</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.050173629408175296</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.16463234655864503</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.029198652334303504</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.3474373816150684E-4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.07872810802086745</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.030702294162890185</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1267539218788447</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.024502966254070033</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0013135484403198595</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.08527453931127754</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.047033422075259616</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.12351565654729546</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.019510774100009145</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.2388377893866785E-5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.08094714885579231</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0386687799538266</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.12322551775775802</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021570596378553932</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.7496696660372355E-4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.08806499896798282</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0499501345427518</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.12617986339321385</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.019446359400628072</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.937266185199552E-6</v>
       </c>
     </row>
   </sheetData>

--- a/SensitivityAnalysis/LeaveOneOut/ContinuousData/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/ContinuousData/loo.xlsx
@@ -51,12 +51,23 @@
     <sheet name="Sheet42" r:id="rId45" sheetId="43"/>
     <sheet name="Sheet43" r:id="rId46" sheetId="44"/>
     <sheet name="Sheet44" r:id="rId47" sheetId="45"/>
+    <sheet name="Sheet45" r:id="rId48" sheetId="46"/>
+    <sheet name="Sheet46" r:id="rId49" sheetId="47"/>
+    <sheet name="Sheet47" r:id="rId50" sheetId="48"/>
+    <sheet name="Sheet48" r:id="rId51" sheetId="49"/>
+    <sheet name="Sheet49" r:id="rId52" sheetId="50"/>
+    <sheet name="Sheet50" r:id="rId53" sheetId="51"/>
+    <sheet name="Sheet51" r:id="rId54" sheetId="52"/>
+    <sheet name="Sheet52" r:id="rId55" sheetId="53"/>
+    <sheet name="Sheet53" r:id="rId56" sheetId="54"/>
+    <sheet name="Sheet54" r:id="rId57" sheetId="55"/>
+    <sheet name="Sheet55" r:id="rId58" sheetId="56"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="22">
   <si>
     <t>SNPS</t>
   </si>
@@ -7844,6 +7855,774 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.931909497717575</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7205324435091726</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.1432865519259776</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.10784543582061351</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.5645886360716805E-18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.1036146599961594</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9948732416408018</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.212356078351517</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05548031548742733</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.772904888565285E-88</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0790210334205437</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7758044558971378</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.3822376109439496</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1547023354711255</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.062614145254206E-12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7868648588199109</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5844159680312841</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9893137496085376</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1032902504023606</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.5764149098300926E-14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9303581359657095</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6932669036535268</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.1674493682778921</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.12096491444499118</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.458293396460425E-14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8484298115366344</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6468308759707988</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.05002874710247</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.10285659977848759</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.6017144633827882E-16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.926502393831458</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.694700918220645</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.1583038694422712</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.11826605898510875</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.723952329451961E-15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.03574643494360698</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-9.362342688830558E-4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.07242910415609702</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.018715647557392873</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.056136322200357816</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.03788802322449598</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.008300182404774835</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.08407622885376678</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02356541103534225</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.10788312224833592</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0210755084763154</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.03460512455320848</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07675614150583929</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.028408486239553003</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.45816386868009784</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.02330092790822724</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.02382467943685371</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.07042653525330819</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.024043677216878036</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.33249114127995855</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.03592884876278468</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-9.47355027298924E-4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.07280505255286829</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.018814389688818167</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.056178638620242236</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.03277163786907704</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.008695338254828752</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.07423861399298283</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021156620471380505</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.12138134785585086</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.03824289144676515</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.001369041742082265</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07511674115144804</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.018813188624838207</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.04207573311274741</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05915991830250599</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.017502068484797483</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.10081776812021451</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.021254005009034953</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005378057859113937</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.07383252297541545</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.020174186268397523</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1274908596824334</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.027376702401539763</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.006998602540540138</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.06008411711873482</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.010602424843004402</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.13077065908047403</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.036064562225377156</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.09571034133547288</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.03334772661850328</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.014387893530977601</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.08108334676798415</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.02435490823953106</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.17092411156594092</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.05932116226417794</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.012526049084507385</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1061162754438485</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.023875057744729877</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.012967886176374809</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04367817123843474</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0016742090306944638</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.08568213344617501</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021430592963132794</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.041537695036630046</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.06228971549915245</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.02493835687245556</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.09964107412584934</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01905681562586576</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.00108068793473313</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.2237771824735491</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.30798399463634796</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.13957037031075026</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0429626592667341</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.902260466411541E-7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.255000235497851</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.36231052729206187</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.14768994370364014</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05475014887459738</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.200321976539395E-6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.2806620317265825</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.4028510227756668</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.15847304067749818</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.06234132196381854</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.730986624013611E-6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.1789547426811224</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.27762403989752127</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.08028544546472352</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.050341478171632086</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.7824224186246147E-4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.2245417779223599</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3189007540209645</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.1301828018237553</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.048142334744186034</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.099357426874473E-6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.17636520822077706</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2165434513845057</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.13618696505704841</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.020499103654963588</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.728279681350265E-18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.22738540533078497</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.31539113848878664</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.1393796721727833</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04490088426428656</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.101981570949229E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -8029,6 +8808,1350 @@
       </c>
       <c r="G8" t="n">
         <v>7.317347859252314E-5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.2812374948697123</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.20488944667524825</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.35758554306417634</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.038953085813502056</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.202473156067034E-13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.3173269449858093</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.22697045380371678</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.40768343616790187</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.046100250603108434</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.843635417069699E-12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3028813031924378</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1764188658600705</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.42934374052480506</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0645216517001874</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.675756816353185E-6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2279578194451356</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1564957494077181</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2994198894825531</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.03646023981500894</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.046318785865935E-10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2822101172910578</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.19690737446284876</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.36751286011926687</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.043521807565412796</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.912213482755919E-11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.24510061682398304</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.18557860667744114</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.30462262697052495</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.030368372523745878</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.977208568845532E-16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.28537937399746277</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.20941898419161908</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.36133976380330646</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.038755300921348816</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.7898649647692223E-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.15092675330312147</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.22466237309051135</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.0771911335157316</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03762021417723973</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.024411777590431E-5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.16936339486517427</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.2688085477686283</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.06991824196172024</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.050737322909925525</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.437051631537243E-4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.20968932450422723</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.30867514834060994</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.11070350066784453</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05050297134509321</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.295540969296039E-5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.12063569370627553</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.21541481326924844</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.025856574143302627</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04835669365457801</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.012606182450557162</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.15102008038368772</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.23388938150984118</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.06815077925753427</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.042280255676608904</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.544252291696689E-4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.1102128461308563</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1510898514728174</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.06933584078889522</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.020855614970388306</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.2600402911205414E-7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.15428962426236992</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.2305449711433638</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.07803427738137601</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03890578922499689</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.317347859252314E-5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.12179124549771227</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0712413738363865</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.17234111715903805</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.025790750847615188</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.3321091923976777E-6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.14193362279383384</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.07862172665337341</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.20524551893429427</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03230198782676553</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.1130461588914655E-5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.13097587098617386</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.046030252000322805</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.21592148997202493</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.043339601523393396</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.002510417419464597</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.08873067323848802</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.037664705442111916</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1397966410348641</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.026054065202232704</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.601002563641802E-4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.12195729256367031</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.06516468084705548</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.17874990428028514</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.028975822304395323</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.565795339292935E-5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.10045632591607576</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05494718246013619</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.14596546937201532</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.02321895074282631</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.5151107245201292E-5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.12529923753747682</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.07963078922584929</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.17096768584910435</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.023300228730422208</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.548659265496716E-8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.02943254833946728</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.00789026014729145</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.066755356826226</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.019042249227938127</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.12219044078354165</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.006038298431212163</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.0409549285530711</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.05303152541549542</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02397613621647105</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8011599573113087</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.011005415510499347</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.045646480797575044</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.06765731181857373</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.028904028728609383</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7033834600870473</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.05464478722882384</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.006696282401525887</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1025932920561218</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.024463522871070387</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02550116061670136</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.029695401088564846</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.007824399891831528</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06721520206896123</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.019142755602243048</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.12083926297411568</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04213990920617099</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-5.082730421731435E-5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0843306457165593</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021525885974687912</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05027241324072354</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.029147255258514443</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.00837006480121967</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.06666457531824856</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.019141489826394957</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.12782712622792985</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.020269808751112006</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.06211246090909776</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.021572843406873744</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.021348291917339668</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.342375764385139</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.015680918185453085</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.06835413254279454</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.03699229617188837</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.026874088957827277</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5595595798493709</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.00810748296966204</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.0716198035736233</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.05540483763429921</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03240424520610268</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8024340975533453</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.023408393025224284</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.07717749819161647</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0303607121411679</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.027433216921628666</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.39350045729598154</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.017335616910070125</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.05939843562262746</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.024727201802487216</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.021460621792121094</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.419213059446973</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.024189970211720948</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.07149534056678505</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.023115400143343155</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.024135393038298012</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3162174121932439</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.023949049765005493</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.06600981755946653</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.018111718029455545</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.021459575405337265</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.26441887108359746</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.018562677370012253</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.018815966845103612</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.055941321585128115</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01907073684444687</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3303748037030675</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.011891371872790915</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.035168112073870966</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.058950855819452794</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.024009940789113206</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6204104704899701</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.04225276108653526</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.014478207509115118</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.09898372968218563</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02894437173247468</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.14434725941906212</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.03117431265869525</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.01684904098362845</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.07919766630101895</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.024501711042001887</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2032551596167816</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.01591760197115121</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.02165838299449708</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0534935869367995</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.019171420900840966</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.40638183097990344</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.01936384861414428</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.022890962327029543</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0616186595553181</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.021558577010802972</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3690805468693195</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01907338960360021</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.018500373993472412</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.05664715320067283</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01917028754952685</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.31976281558183184</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.08969700388260139</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.05056345920535811</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.12883054855984466</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01996609422308331</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.0403087638715485E-6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.10284315912275133</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.053570179412439495</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.15211613883306316</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.025139275362403995</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.2963624260596356E-5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.11023901809636232</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.050838782479662226</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1696392537130624</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03030624266158168</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.7529506229688374E-4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.08110647114016263</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.030829458900992812</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.13138348337933245</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.025651536856719295</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0015676695212573808</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.08772151477965855</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.048381481117834184</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1270615484414829</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.020071445745828757</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.2398325551345761E-5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.08351903680913872</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.03928048971589261</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.12775758390238484</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.022570687292472504</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.153175725380216E-4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0902197469488535</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.05088250484816266</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.12955698904954432</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.020070021479944307</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.948853523270882E-6</v>
       </c>
     </row>
   </sheetData>
